--- a/artfynd/A 6381-2023 artfynd.xlsx
+++ b/artfynd/A 6381-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6381-2023 artfynd.xlsx
+++ b/artfynd/A 6381-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6772428</v>
+        <v>6762494</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,26 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnsudden, NV om (*gk* /stjälk/), Upl</t>
+          <t>Hasselbacken (*gk* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717937.3151116994</v>
+        <v>717910</v>
       </c>
       <c r="R2" t="n">
-        <v>6645847.125081277</v>
+        <v>6645638</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,32 +740,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>AB-Nor-0611</t>
+          <t>AB-Nor-0610</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-06-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-05-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Finnsudden i Södra Rörvik / 2 grupper: 11 blom.+13 ej blom. stjälkar resp 9 blom.+ 9 ej blom. Stjälkar / Hot/anm:: Oförändrad frekvens.</t>
+          <t>objekt 04:1</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Stefan Eklund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16882756</v>
+        <v>6767947</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,28 +814,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hasselbacken (*gk* /stjälk/), Upl</t>
+          <t>Finnsudden, NV om (*gk* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717909.8435298892</v>
+        <v>717937</v>
       </c>
       <c r="R3" t="n">
-        <v>6645637.763303566</v>
+        <v>6645847</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,36 +860,26 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>AB-Nor-0610</t>
+          <t>AB-Nor-0611</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-06-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-06-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-06-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Observatörer Joakim Ekman och Ebbe Zachrisson. Lokalen belägen i brantare sluttning ned mot Rörviksfjärden, delvis ledningsgata. Ingen guckusko kunde återfinnas men lämpliga biotoper finns. Oklart om lokalen existerar i sinnevärden eller är en sammanblandning med lokalen vid Finnsudden. Smal brant glänta i skogsmark.</t>
+          <t>1 grupp på en halv kvadratmeter, med 8 blommande och 10 ej blommande stjälkar. Växande alldeles på N-sid av äldre djupt skogsmaskinspår i frisk, gles blandskog. Spontan förekomst, känd sedan länge av markägaren som visade lokalen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -928,20 +887,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog, sydvänd sluttning</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>AB-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson, Joakim Ekman</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 6381-2023 artfynd.xlsx
+++ b/artfynd/A 6381-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6762494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6767947</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>